--- a/public/exports-from-60-with-coowners/29189854.xlsx
+++ b/public/exports-from-60-with-coowners/29189854.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">

--- a/public/exports-from-60-with-coowners/29189854.xlsx
+++ b/public/exports-from-60-with-coowners/29189854.xlsx
@@ -4901,12 +4901,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Museum Sønderjylland</t>
+          <t xml:space="preserve">Aabenraa Kommune</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4916,50 +4916,50 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">H P Hanssens Gade 33</t>
+          <t xml:space="preserve">Åbjerg 8B</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6340</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">5776368</t>
+          <t xml:space="preserve">5263733</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J66">
-        <v>839</v>
+        <v>534</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t xml:space="preserve">311178681</t>
+          <t xml:space="preserve">311358212</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Vh-consult</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-25</t>
+          <t xml:space="preserve">2029-02-06</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -4991,40 +4991,40 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åbjerg 8B</t>
+          <t xml:space="preserve">Skelbækvej 2</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">6340</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">5263733</t>
+          <t xml:space="preserve">5777441</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J67">
-        <v>534</v>
+        <v>13747</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t xml:space="preserve">311358212</t>
+          <t xml:space="preserve">311384248</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vh-consult</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-02-06</t>
+          <t xml:space="preserve">2029-06-24</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5066,40 +5066,40 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skelbækvej 2</t>
+          <t xml:space="preserve">Valdemarsgade 11</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6330</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">5777441</t>
+          <t xml:space="preserve">10006074</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J68">
-        <v>13747</v>
+        <v>381</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t xml:space="preserve">311384248</t>
+          <t xml:space="preserve">311385901</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">Elmlund Erhverv v/Carsten E Rasmussen</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-06-24</t>
+          <t xml:space="preserve">2029-07-02</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5141,40 +5141,40 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdemarsgade 11</t>
+          <t xml:space="preserve">Skovbrynet 2</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">6330</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">10006074</t>
+          <t xml:space="preserve">5256718</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J69">
-        <v>381</v>
+        <v>7580</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311385901</t>
+          <t xml:space="preserve">311434534</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmlund Erhverv v/Carsten E Rasmussen</t>
+          <t xml:space="preserve">Vh-consult</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-07-02</t>
+          <t xml:space="preserve">2030-04-27</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5231,15 +5231,15 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="J70">
-        <v>7580</v>
+        <v>188</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311434534</t>
+          <t xml:space="preserve">311436528</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-04-27</t>
+          <t xml:space="preserve">2030-05-06</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovbrynet 2</t>
+          <t xml:space="preserve">Kirkegade 23</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5301,20 +5301,20 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">5256718</t>
+          <t xml:space="preserve">5250298</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J71">
-        <v>188</v>
+        <v>626</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311436528</t>
+          <t xml:space="preserve">311498610</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-05-06</t>
+          <t xml:space="preserve">2031-02-25</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5366,17 +5366,17 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 23</t>
+          <t xml:space="preserve">Dronning Margrethes Vej 3</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">5250298</t>
+          <t xml:space="preserve">5777076</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -5385,21 +5385,21 @@
         </is>
       </c>
       <c r="J72">
-        <v>626</v>
+        <v>452</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311498610</t>
+          <t xml:space="preserve">311522368</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vh-consult</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-02-25</t>
+          <t xml:space="preserve">2031-05-25</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5441,30 +5441,30 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronning Margrethes Vej 3</t>
+          <t xml:space="preserve">Hovedgaden 78</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6360</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">5777076</t>
+          <t xml:space="preserve">5242501</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J73">
-        <v>452</v>
+        <v>1439</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311522368</t>
+          <t xml:space="preserve">311522367</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5531,11 +5531,11 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J74">
-        <v>1439</v>
+        <v>1390</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 78</t>
+          <t xml:space="preserve">Nørreagervej 45</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5606,11 +5606,11 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J75">
-        <v>1390</v>
+        <v>3702</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørreagervej 45</t>
+          <t xml:space="preserve">Tinglev Midt 2</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5676,20 +5676,20 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">5242501</t>
+          <t xml:space="preserve">9643472</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J76">
-        <v>3702</v>
+        <v>2743</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t xml:space="preserve">311522367</t>
+          <t xml:space="preserve">311522375</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tinglev Midt 2</t>
+          <t xml:space="preserve">Tinglev Midt 4</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5756,15 +5756,15 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J77">
-        <v>2743</v>
+        <v>1267</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t xml:space="preserve">311522375</t>
+          <t xml:space="preserve">311522371</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tinglev Midt 4</t>
+          <t xml:space="preserve">Grønnevej 32</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5831,25 +5831,25 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J78">
-        <v>1267</v>
+        <v>847</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t xml:space="preserve">311522371</t>
+          <t xml:space="preserve">311578480</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-05-25</t>
+          <t xml:space="preserve">2032-02-13</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnevej 32</t>
+          <t xml:space="preserve">Tinglev Midt 2</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J79">
@@ -5914,7 +5914,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t xml:space="preserve">311578480</t>
+          <t xml:space="preserve">311578481</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tinglev Midt 2</t>
+          <t xml:space="preserve">Grønnevej 32</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5981,15 +5981,15 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J80">
-        <v>847</v>
+        <v>602</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t xml:space="preserve">311578481</t>
+          <t xml:space="preserve">311578773</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-13</t>
+          <t xml:space="preserve">2032-02-15</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6041,40 +6041,40 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnevej 32</t>
+          <t xml:space="preserve">Østermarkvej 1P</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">6360</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">9643472</t>
+          <t xml:space="preserve">8073695</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J81">
-        <v>602</v>
+        <v>555</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t xml:space="preserve">311578773</t>
+          <t xml:space="preserve">311601866</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-15</t>
+          <t xml:space="preserve">2032-05-20</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6116,40 +6116,40 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østermarkvej 1P</t>
+          <t xml:space="preserve">Kalveknækket 47</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6340</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">8073695</t>
+          <t xml:space="preserve">5262648</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J82">
-        <v>555</v>
+        <v>2330</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601866</t>
+          <t xml:space="preserve">311644250</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-20</t>
+          <t xml:space="preserve">2032-11-22</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6176,12 +6176,12 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aabenraa Kommune</t>
+          <t xml:space="preserve">FONDEN TIL BEVARELSE AF GAMLE BYGNINGER I TINGLEV</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -6191,30 +6191,30 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalveknækket 47</t>
+          <t xml:space="preserve">Hovedgaden 105B</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t xml:space="preserve">6340</t>
+          <t xml:space="preserve">6360</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">5262648</t>
+          <t xml:space="preserve">737580, 5242329</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J83">
-        <v>2330</v>
+        <v>198</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t xml:space="preserve">311644250</t>
+          <t xml:space="preserve">311650398</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6224,7 +6224,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-22</t>
+          <t xml:space="preserve">2032-12-20</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6251,12 +6251,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">FONDEN TIL BEVARELSE AF GAMLE BYGNINGER I TINGLEV</t>
+          <t xml:space="preserve">Aabenraa Kommune</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -6266,30 +6266,30 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 105B</t>
+          <t xml:space="preserve">Molevej 18A</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t xml:space="preserve">6360</t>
+          <t xml:space="preserve">6340</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">737580, 5242329</t>
+          <t xml:space="preserve">5262575</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J84">
-        <v>198</v>
+        <v>336</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650398</t>
+          <t xml:space="preserve">311650394</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -6341,17 +6341,17 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molevej 18A</t>
+          <t xml:space="preserve">Smedefod 4B</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t xml:space="preserve">6340</t>
+          <t xml:space="preserve">6392</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">5262575</t>
+          <t xml:space="preserve">5248731</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -6360,11 +6360,11 @@
         </is>
       </c>
       <c r="J85">
-        <v>336</v>
+        <v>316</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650394</t>
+          <t xml:space="preserve">311650397</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6416,17 +6416,17 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedefod 4B</t>
+          <t xml:space="preserve">Stadionalle 1</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">6392</t>
+          <t xml:space="preserve">6340</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">5248731</t>
+          <t xml:space="preserve">9069454</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -6435,11 +6435,11 @@
         </is>
       </c>
       <c r="J86">
-        <v>316</v>
+        <v>159</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650397</t>
+          <t xml:space="preserve">311650396</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6491,17 +6491,17 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 1</t>
+          <t xml:space="preserve">Åbovej 12A</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t xml:space="preserve">6340</t>
+          <t xml:space="preserve">6372</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">9069454</t>
+          <t xml:space="preserve">312951, 312952</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -6510,11 +6510,11 @@
         </is>
       </c>
       <c r="J87">
-        <v>159</v>
+        <v>1169</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650396</t>
+          <t xml:space="preserve">311650395</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -6566,17 +6566,17 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åbovej 12A</t>
+          <t xml:space="preserve">Skolegade 2</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">6372</t>
+          <t xml:space="preserve">6340</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">312951, 312952</t>
+          <t xml:space="preserve">100044523</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -6585,11 +6585,11 @@
         </is>
       </c>
       <c r="J88">
-        <v>1169</v>
+        <v>334</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311650395</t>
+          <t xml:space="preserve">311653972</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-20</t>
+          <t xml:space="preserve">2033-01-13</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6656,11 +6656,11 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J89">
-        <v>334</v>
+        <v>144</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -6716,40 +6716,40 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 2</t>
+          <t xml:space="preserve">Skovbrynet 4</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t xml:space="preserve">6340</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">100044523</t>
+          <t xml:space="preserve">5256718</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="J90">
-        <v>144</v>
+        <v>778</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311653972</t>
+          <t xml:space="preserve">311654332</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Vh-consult</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-13</t>
+          <t xml:space="preserve">2033-01-16</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6806,15 +6806,15 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="J91">
-        <v>778</v>
+        <v>665</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654332</t>
+          <t xml:space="preserve">311654333</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6866,40 +6866,40 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovbrynet 4</t>
+          <t xml:space="preserve">Kalveknækket 45A</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6340</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">5256718</t>
+          <t xml:space="preserve">5262778</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J92">
-        <v>665</v>
+        <v>558</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654333</t>
+          <t xml:space="preserve">311654619</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vh-consult</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-16</t>
+          <t xml:space="preserve">2033-01-18</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalveknækket 45A</t>
+          <t xml:space="preserve">Kalveknækket 45B</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6956,11 +6956,11 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J93">
-        <v>558</v>
+        <v>103</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalveknækket 45B</t>
+          <t xml:space="preserve">Kalveknækket 45C</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -7031,11 +7031,11 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J94">
-        <v>103</v>
+        <v>198</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -7106,11 +7106,11 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J95">
-        <v>198</v>
+        <v>167</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kalveknækket 45C</t>
+          <t xml:space="preserve">Flensborgvej 9B</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -7176,20 +7176,20 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">5262778</t>
+          <t xml:space="preserve">5263423</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J96">
-        <v>167</v>
+        <v>348</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654619</t>
+          <t xml:space="preserve">311661161</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-18</t>
+          <t xml:space="preserve">2033-02-20</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7241,17 +7241,17 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flensborgvej 9B</t>
+          <t xml:space="preserve">Grønnevej 41</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t xml:space="preserve">6340</t>
+          <t xml:space="preserve">6360</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">5263423</t>
+          <t xml:space="preserve">5242614</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -7260,11 +7260,11 @@
         </is>
       </c>
       <c r="J97">
-        <v>348</v>
+        <v>158</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661161</t>
+          <t xml:space="preserve">311661165</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnevej 41</t>
+          <t xml:space="preserve">Mads Clausens Vej 130</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">5242614</t>
+          <t xml:space="preserve">5243879</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -7335,11 +7335,11 @@
         </is>
       </c>
       <c r="J98">
-        <v>158</v>
+        <v>814</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661165</t>
+          <t xml:space="preserve">311661163</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -7391,30 +7391,30 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mads Clausens Vej 130</t>
+          <t xml:space="preserve">Smedefod 10A</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t xml:space="preserve">6360</t>
+          <t xml:space="preserve">6392</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">5243879</t>
+          <t xml:space="preserve">5248692</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J99">
-        <v>814</v>
+        <v>3970</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661163</t>
+          <t xml:space="preserve">311661158</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -7481,15 +7481,15 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J100">
-        <v>3970</v>
+        <v>218</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661158</t>
+          <t xml:space="preserve">311661159</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -7541,30 +7541,30 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Smedefod 10A</t>
+          <t xml:space="preserve">Tværvejen 4</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">6392</t>
+          <t xml:space="preserve">6360</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">5248692</t>
+          <t xml:space="preserve">5242741</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J101">
-        <v>218</v>
+        <v>338</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661159</t>
+          <t xml:space="preserve">311661169</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tværvejen 4</t>
+          <t xml:space="preserve">Hovedgaden 78</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">5242741</t>
+          <t xml:space="preserve">5242501</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -7635,11 +7635,11 @@
         </is>
       </c>
       <c r="J102">
-        <v>338</v>
+        <v>1466</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661169</t>
+          <t xml:space="preserve">311661648</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7649,7 +7649,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-20</t>
+          <t xml:space="preserve">2033-02-22</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 78</t>
+          <t xml:space="preserve">Hovedgaden 82</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -7701,7 +7701,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">5242501</t>
+          <t xml:space="preserve">5242835</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -7710,11 +7710,11 @@
         </is>
       </c>
       <c r="J103">
-        <v>1466</v>
+        <v>357</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661648</t>
+          <t xml:space="preserve">311661649</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -7766,17 +7766,17 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 82</t>
+          <t xml:space="preserve">Nørrekær 15</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">6360</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">5242835</t>
+          <t xml:space="preserve">9073631</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -7785,11 +7785,11 @@
         </is>
       </c>
       <c r="J104">
-        <v>357</v>
+        <v>3104</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661649</t>
+          <t xml:space="preserve">311661636</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrekær 15</t>
+          <t xml:space="preserve">Skolegade 12A</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">9073631</t>
+          <t xml:space="preserve">5270230</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -7860,11 +7860,11 @@
         </is>
       </c>
       <c r="J105">
-        <v>3104</v>
+        <v>1798</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661636</t>
+          <t xml:space="preserve">311661646</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7931,11 +7931,11 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J106">
-        <v>1798</v>
+        <v>123</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
@@ -8006,11 +8006,11 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J107">
-        <v>123</v>
+        <v>89</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
@@ -8081,11 +8081,11 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J108">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 12A</t>
+          <t xml:space="preserve">Skolegade 12B</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -8156,11 +8156,11 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J109">
-        <v>130</v>
+        <v>516</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 12B</t>
+          <t xml:space="preserve">Skolegade 12C</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -8231,15 +8231,15 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J110">
-        <v>516</v>
+        <v>409</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661646</t>
+          <t xml:space="preserve">311661642</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -8291,30 +8291,30 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 12C</t>
+          <t xml:space="preserve">Åbovej 27A</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6372</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">5270230</t>
+          <t xml:space="preserve">5235664</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J111">
-        <v>409</v>
+        <v>319</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661642</t>
+          <t xml:space="preserve">311661637</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8366,17 +8366,17 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åbovej 27A</t>
+          <t xml:space="preserve">Sønderskovvej 25</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">6372</t>
+          <t xml:space="preserve">6360</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">5235664</t>
+          <t xml:space="preserve">9734086</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -8385,11 +8385,11 @@
         </is>
       </c>
       <c r="J112">
-        <v>319</v>
+        <v>829</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661637</t>
+          <t xml:space="preserve">311661950</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-22</t>
+          <t xml:space="preserve">2033-02-23</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8456,15 +8456,15 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J113">
-        <v>829</v>
+        <v>125</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661950</t>
+          <t xml:space="preserve">311661951</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderskovvej 25</t>
+          <t xml:space="preserve">Sønderskovvej 27</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -8531,15 +8531,15 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J114">
-        <v>125</v>
+        <v>364</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661951</t>
+          <t xml:space="preserve">311661950</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -8591,30 +8591,30 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderskovvej 27</t>
+          <t xml:space="preserve">Biblioteksstrædet 1</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">6360</t>
+          <t xml:space="preserve">6372</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">9734086</t>
+          <t xml:space="preserve">5235842</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J115">
-        <v>364</v>
+        <v>112</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661950</t>
+          <t xml:space="preserve">311667971</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-23</t>
+          <t xml:space="preserve">2033-03-21</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Biblioteksstrædet 1</t>
+          <t xml:space="preserve">Engløkke 30</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">5235842</t>
+          <t xml:space="preserve">5235995</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -8685,11 +8685,11 @@
         </is>
       </c>
       <c r="J116">
-        <v>112</v>
+        <v>4022</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">311667971</t>
+          <t xml:space="preserve">311667969</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -8741,30 +8741,30 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engløkke 30</t>
+          <t xml:space="preserve">Kirkegårdsvej 2A</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">6372</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">5235995</t>
+          <t xml:space="preserve">9319699</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J117">
-        <v>4022</v>
+        <v>148</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">311667969</t>
+          <t xml:space="preserve">311668057</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegårdsvej 2A</t>
+          <t xml:space="preserve">Kirkegårdsvej 2B</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J118">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegårdsvej 2B</t>
+          <t xml:space="preserve">Kliplev Hovedgade 6A</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -8906,20 +8906,20 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J119">
-        <v>148</v>
+        <v>1216</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">311668057</t>
+          <t xml:space="preserve">311667988</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kliplev Hovedgade 6A</t>
+          <t xml:space="preserve">Kliplev Hovedgade 6B</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -8981,20 +8981,20 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J120">
-        <v>1216</v>
+        <v>524</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">311667988</t>
+          <t xml:space="preserve">311667989</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -9041,30 +9041,30 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kliplev Hovedgade 6B</t>
+          <t xml:space="preserve">Nørreagervej 58</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6360</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">9319699</t>
+          <t xml:space="preserve">5243876</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J121">
-        <v>524</v>
+        <v>1027</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">311667989</t>
+          <t xml:space="preserve">311668049</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -9116,30 +9116,30 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørreagervej 58</t>
+          <t xml:space="preserve">Strandvej 12</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t xml:space="preserve">6360</t>
+          <t xml:space="preserve">6340</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">5243876</t>
+          <t xml:space="preserve">5268468</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J122">
-        <v>1027</v>
+        <v>85</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311668049</t>
+          <t xml:space="preserve">311668055</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -9191,30 +9191,30 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvej 12</t>
+          <t xml:space="preserve">Østermarkvej 1A</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t xml:space="preserve">6340</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">5268468</t>
+          <t xml:space="preserve">8073695</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J123">
-        <v>85</v>
+        <v>406</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311668055</t>
+          <t xml:space="preserve">311668436</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-21</t>
+          <t xml:space="preserve">2033-03-22</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9266,7 +9266,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østermarkvej 1A</t>
+          <t xml:space="preserve">Østermarkvej 1B</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -9281,15 +9281,15 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J124">
-        <v>406</v>
+        <v>935</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311668436</t>
+          <t xml:space="preserve">311668438</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -9341,30 +9341,30 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østermarkvej 1B</t>
+          <t xml:space="preserve">Bytoften 13</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">8073695</t>
+          <t xml:space="preserve">5274226</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J125">
-        <v>935</v>
+        <v>854</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">311668438</t>
+          <t xml:space="preserve">311670155</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -9374,7 +9374,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-22</t>
+          <t xml:space="preserve">2033-03-29</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9416,30 +9416,30 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bytoften 13</t>
+          <t xml:space="preserve">Hovedgaden 84</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6360</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">5274226</t>
+          <t xml:space="preserve">5242501</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J126">
-        <v>854</v>
+        <v>130</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670155</t>
+          <t xml:space="preserve">311670158</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -9491,30 +9491,30 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 84</t>
+          <t xml:space="preserve">Klostervang 46</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">6360</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">5242501</t>
+          <t xml:space="preserve">5270632</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J127">
-        <v>130</v>
+        <v>608</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670158</t>
+          <t xml:space="preserve">311670156</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -9566,30 +9566,30 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostervang 46</t>
+          <t xml:space="preserve">Kobbermøllevej 14</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6340</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">5270632</t>
+          <t xml:space="preserve">8162582</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J128">
-        <v>608</v>
+        <v>193</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670156</t>
+          <t xml:space="preserve">311670161</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kobbermøllevej 14</t>
+          <t xml:space="preserve">Kobbermøllevej 2</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -9656,7 +9656,7 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J129">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kobbermøllevej 2</t>
+          <t xml:space="preserve">Kobbermøllevej 20</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -9731,7 +9731,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J130">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kobbermøllevej 20</t>
+          <t xml:space="preserve">Kobbermøllevej 26</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -9806,7 +9806,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J131">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kobbermøllevej 26</t>
+          <t xml:space="preserve">Kobbermøllevej 32</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -9881,11 +9881,11 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J132">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
@@ -9941,7 +9941,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kobbermøllevej 32</t>
+          <t xml:space="preserve">Kobbermøllevej 38</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -9956,7 +9956,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J133">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kobbermøllevej 38</t>
+          <t xml:space="preserve">Kobbermøllevej 44</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -10031,7 +10031,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J134">
@@ -10091,7 +10091,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kobbermøllevej 44</t>
+          <t xml:space="preserve">Kobbermøllevej 50A</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -10106,15 +10106,15 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J135">
-        <v>180</v>
+        <v>1072</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670161</t>
+          <t xml:space="preserve">311670165</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kobbermøllevej 50A</t>
+          <t xml:space="preserve">Kobbermøllevej 50B</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -10181,20 +10181,20 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J136">
-        <v>1072</v>
+        <v>408</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670165</t>
+          <t xml:space="preserve">311670164</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M136" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kobbermøllevej 50B</t>
+          <t xml:space="preserve">Kobbermøllevej 50C</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J137">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kobbermøllevej 50C</t>
+          <t xml:space="preserve">Kobbermøllevej 50D</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -10331,7 +10331,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J138">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kobbermøllevej 50D</t>
+          <t xml:space="preserve">Kobbermøllevej 50E</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="J139">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kobbermøllevej 50E</t>
+          <t xml:space="preserve">Kobbermøllevej 8</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -10481,20 +10481,20 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J140">
-        <v>408</v>
+        <v>193</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670164</t>
+          <t xml:space="preserve">311670161</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -10541,17 +10541,17 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kobbermøllevej 8</t>
+          <t xml:space="preserve">Ravsted Skolegade 16</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">6340</t>
+          <t xml:space="preserve">6372</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">8162582</t>
+          <t xml:space="preserve">9345395</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -10560,11 +10560,11 @@
         </is>
       </c>
       <c r="J141">
-        <v>193</v>
+        <v>267</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670161</t>
+          <t xml:space="preserve">311670238</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravsted Skolegade 16</t>
+          <t xml:space="preserve">Ravsted Skolegade 18</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -10631,15 +10631,15 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J142">
-        <v>267</v>
+        <v>2157</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670238</t>
+          <t xml:space="preserve">311670236</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -10691,17 +10691,17 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravsted Skolegade 18</t>
+          <t xml:space="preserve">Varnæs Kirkevej 15</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">6372</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">9345395</t>
+          <t xml:space="preserve">5274894</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -10710,16 +10710,16 @@
         </is>
       </c>
       <c r="J143">
-        <v>2157</v>
+        <v>2071</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670236</t>
+          <t xml:space="preserve">311670153</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -10766,17 +10766,17 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Varnæs Kirkevej 15</t>
+          <t xml:space="preserve">Gammel Søndergade 20A</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6392</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">5274894</t>
+          <t xml:space="preserve">5248471</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -10785,21 +10785,21 @@
         </is>
       </c>
       <c r="J144">
-        <v>2071</v>
+        <v>358</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670153</t>
+          <t xml:space="preserve">311670600</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-29</t>
+          <t xml:space="preserve">2033-03-30</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10856,15 +10856,15 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J145">
-        <v>358</v>
+        <v>862</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670600</t>
+          <t xml:space="preserve">311670599</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -10916,7 +10916,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Søndergade 20A</t>
+          <t xml:space="preserve">Gammel Søndergade 20L</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -10926,20 +10926,20 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">5248471</t>
+          <t xml:space="preserve">8040385</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J146">
-        <v>862</v>
+        <v>470</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670599</t>
+          <t xml:space="preserve">311670603</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -10991,30 +10991,30 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Søndergade 20L</t>
+          <t xml:space="preserve">Kirkegårdsvej 27</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">6392</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">8040385</t>
+          <t xml:space="preserve">5270474</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J147">
-        <v>470</v>
+        <v>242</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670603</t>
+          <t xml:space="preserve">311670944</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-30</t>
+          <t xml:space="preserve">2033-03-31</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -11066,30 +11066,30 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegårdsvej 27</t>
+          <t xml:space="preserve">Slogsherredsvej 27</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6372</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">5270474</t>
+          <t xml:space="preserve">9120321</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J148">
-        <v>242</v>
+        <v>2095</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311670944</t>
+          <t xml:space="preserve">311673018</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -11099,7 +11099,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-31</t>
+          <t xml:space="preserve">2033-04-12</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -11156,11 +11156,11 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J149">
-        <v>2095</v>
+        <v>806</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
@@ -11231,15 +11231,15 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J150">
-        <v>806</v>
+        <v>126</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311673018</t>
+          <t xml:space="preserve">311673019</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -11306,15 +11306,15 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J151">
-        <v>126</v>
+        <v>2646</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311673019</t>
+          <t xml:space="preserve">311673018</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -11351,12 +11351,12 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aabenraa Kommune</t>
+          <t xml:space="preserve">Domea Syd</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -11366,40 +11366,40 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slogsherredsvej 27</t>
+          <t xml:space="preserve">Rise Bygade 50</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">6372</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">9120321</t>
+          <t xml:space="preserve">312318, 312319</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J152">
-        <v>2646</v>
+        <v>926</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311673018</t>
+          <t xml:space="preserve">311678544</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-12</t>
+          <t xml:space="preserve">2033-05-03</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rise Bygade 50</t>
+          <t xml:space="preserve">Rise Bygade 52</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -11456,11 +11456,11 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J153">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
@@ -11516,7 +11516,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rise Bygade 52</t>
+          <t xml:space="preserve">Rise Bygade 54</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -11531,11 +11531,11 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J154">
-        <v>921</v>
+        <v>927</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
@@ -11591,7 +11591,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rise Bygade 54</t>
+          <t xml:space="preserve">Rise Bygade 56</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -11606,11 +11606,11 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J155">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
@@ -11666,7 +11666,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rise Bygade 56</t>
+          <t xml:space="preserve">Rise Bygade 58</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -11681,7 +11681,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J156">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rise Bygade 58</t>
+          <t xml:space="preserve">Rise Bygade 60</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -11756,11 +11756,11 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J157">
-        <v>926</v>
+        <v>963</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rise Bygade 60</t>
+          <t xml:space="preserve">Rise Bygade 62</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -11831,11 +11831,11 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J158">
-        <v>963</v>
+        <v>927</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
@@ -11876,12 +11876,12 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Domea Syd</t>
+          <t xml:space="preserve">Aabenraa Kommune</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -11891,40 +11891,40 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rise Bygade 62</t>
+          <t xml:space="preserve">Bovvej 2A</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6330</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">312318, 312319</t>
+          <t xml:space="preserve">9069219</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J159">
-        <v>927</v>
+        <v>244</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311678544</t>
+          <t xml:space="preserve">311678991</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-03</t>
+          <t xml:space="preserve">2033-05-08</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11981,11 +11981,11 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J160">
-        <v>244</v>
+        <v>314</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bovvej 2A</t>
+          <t xml:space="preserve">Bovvej 2B</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -12056,11 +12056,11 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J161">
-        <v>314</v>
+        <v>510</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
@@ -12131,11 +12131,11 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J162">
-        <v>510</v>
+        <v>268</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
@@ -12206,11 +12206,11 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J163">
-        <v>268</v>
+        <v>153</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
@@ -12266,7 +12266,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bovvej 2B</t>
+          <t xml:space="preserve">Bovvej 4</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -12276,20 +12276,20 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">9069219</t>
+          <t xml:space="preserve">5260034</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J164">
-        <v>153</v>
+        <v>1438</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311678991</t>
+          <t xml:space="preserve">311679002</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -12341,7 +12341,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bovvej 4</t>
+          <t xml:space="preserve">Padborgvej 55B</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -12351,20 +12351,20 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">5260034</t>
+          <t xml:space="preserve">5260044</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J165">
-        <v>1438</v>
+        <v>1419</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311679002</t>
+          <t xml:space="preserve">311679338</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -12374,7 +12374,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-08</t>
+          <t xml:space="preserve">2033-05-09</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12416,7 +12416,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Padborgvej 55B</t>
+          <t xml:space="preserve">Jernbanegade 14</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -12426,20 +12426,20 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">5260044</t>
+          <t xml:space="preserve">5259724</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J166">
-        <v>1419</v>
+        <v>438</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311679338</t>
+          <t xml:space="preserve">311680033</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-09</t>
+          <t xml:space="preserve">2033-05-11</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanegade 14</t>
+          <t xml:space="preserve">Jernbanegade 36A</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">5259724</t>
+          <t xml:space="preserve">5260026</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -12510,11 +12510,11 @@
         </is>
       </c>
       <c r="J167">
-        <v>438</v>
+        <v>415</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311680033</t>
+          <t xml:space="preserve">311680035</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -12551,12 +12551,12 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aabenraa Kommune</t>
+          <t xml:space="preserve">Naturstyrelsen</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanegade 36A</t>
+          <t xml:space="preserve">Lejrvejen 13</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -12576,20 +12576,20 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">5260026</t>
+          <t xml:space="preserve">737452, 9069252</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">89</t>
         </is>
       </c>
       <c r="J168">
-        <v>415</v>
+        <v>629</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311680035</t>
+          <t xml:space="preserve">311680150</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -12626,12 +12626,12 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturstyrelsen</t>
+          <t xml:space="preserve">Aabenraa Kommune</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lejrvejen 13</t>
+          <t xml:space="preserve">Lejrvejen 17</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -12651,20 +12651,20 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">737452, 9069252</t>
+          <t xml:space="preserve">7991181</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">89</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J169">
-        <v>629</v>
+        <v>72</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311680150</t>
+          <t xml:space="preserve">311680144</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -12716,7 +12716,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lejrvejen 17</t>
+          <t xml:space="preserve">Lejrvejen 21</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -12731,7 +12731,7 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J170">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lejrvejen 21</t>
+          <t xml:space="preserve">Lejrvejen 25</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -12806,7 +12806,7 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J171">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lejrvejen 25</t>
+          <t xml:space="preserve">Lejrvejen 35</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -12881,7 +12881,7 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J172">
@@ -12941,7 +12941,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lejrvejen 35</t>
+          <t xml:space="preserve">Lejrvejen 39</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -12956,7 +12956,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J173">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lejrvejen 39</t>
+          <t xml:space="preserve">Lejrvejen 43</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -13031,11 +13031,11 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J174">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lejrvejen 43</t>
+          <t xml:space="preserve">Lejrvejen 45</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -13106,7 +13106,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J175">
@@ -13166,7 +13166,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lejrvejen 45</t>
+          <t xml:space="preserve">Lejrvejen 49</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -13181,11 +13181,11 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J176">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lejrvejen 49</t>
+          <t xml:space="preserve">Lejrvejen 53</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J177">
@@ -13316,7 +13316,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lejrvejen 53</t>
+          <t xml:space="preserve">Lejrvejen 59</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -13331,7 +13331,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J178">
@@ -13391,7 +13391,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lejrvejen 59</t>
+          <t xml:space="preserve">Lejrvejen 63</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -13406,7 +13406,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J179">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lejrvejen 63</t>
+          <t xml:space="preserve">Lejrvejen 67</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -13481,11 +13481,11 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J180">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lejrvejen 67</t>
+          <t xml:space="preserve">Padborgvej 20A</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -13551,20 +13551,20 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">7991181</t>
+          <t xml:space="preserve">9410204</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J181">
-        <v>93</v>
+        <v>1971</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311680144</t>
+          <t xml:space="preserve">311691896</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -13574,7 +13574,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-11</t>
+          <t xml:space="preserve">2033-06-30</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13616,7 +13616,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Padborgvej 20A</t>
+          <t xml:space="preserve">Padborgvej 20B</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -13631,20 +13631,20 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J182">
-        <v>1971</v>
+        <v>1232</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311691896</t>
+          <t xml:space="preserve">311691894</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -13691,7 +13691,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Padborgvej 20B</t>
+          <t xml:space="preserve">Padborgvej 20C</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -13706,11 +13706,11 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J183">
-        <v>1232</v>
+        <v>451</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Padborgvej 20C</t>
+          <t xml:space="preserve">Padborgvej 20D</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -13781,11 +13781,11 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J184">
-        <v>451</v>
+        <v>573</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Padborgvej 20D</t>
+          <t xml:space="preserve">Plantagevej 2B</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -13851,30 +13851,30 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">9410204</t>
+          <t xml:space="preserve">5260531</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J185">
-        <v>573</v>
+        <v>1842</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311691894</t>
+          <t xml:space="preserve">311696895</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-30</t>
+          <t xml:space="preserve">2033-07-27</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plantagevej 2B</t>
+          <t xml:space="preserve">Plantagevej 2C</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -13926,7 +13926,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">5260531</t>
+          <t xml:space="preserve">8597947</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -13935,11 +13935,11 @@
         </is>
       </c>
       <c r="J186">
-        <v>1842</v>
+        <v>150</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311696895</t>
+          <t xml:space="preserve">311696894</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -13991,7 +13991,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plantagevej 2C</t>
+          <t xml:space="preserve">Kempesteens Vej 70</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -14001,7 +14001,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">8597947</t>
+          <t xml:space="preserve">5260533</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -14010,11 +14010,11 @@
         </is>
       </c>
       <c r="J187">
-        <v>150</v>
+        <v>492</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311696894</t>
+          <t xml:space="preserve">311706365</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -14024,7 +14024,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-07-27</t>
+          <t xml:space="preserve">2033-09-11</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -14051,12 +14051,12 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aabenraa Kommune</t>
+          <t xml:space="preserve">BoligSyd</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -14066,40 +14066,40 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kempesteens Vej 70</t>
+          <t xml:space="preserve">Mejerihaven 1</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">6330</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">5260533</t>
+          <t xml:space="preserve">312368, 312369</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J188">
-        <v>492</v>
+        <v>450</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706365</t>
+          <t xml:space="preserve">311707108</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-11</t>
+          <t xml:space="preserve">2033-09-12</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -14131,7 +14131,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t xml:space="preserve">BoligSyd</t>
+          <t xml:space="preserve">KOLSTRUP BOLIGFORENING</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mejerihaven 1</t>
+          <t xml:space="preserve">Lergård 100</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -14151,20 +14151,20 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">312368, 312369</t>
+          <t xml:space="preserve">421261, 421262</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J189">
-        <v>450</v>
+        <v>1074</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311707108</t>
+          <t xml:space="preserve">311707964</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -14174,7 +14174,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-12</t>
+          <t xml:space="preserve">2033-09-15</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lergård 100</t>
+          <t xml:space="preserve">Lergård 102</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -14231,7 +14231,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J190">
@@ -14291,7 +14291,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lergård 102</t>
+          <t xml:space="preserve">Lergård 104</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -14306,7 +14306,7 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J191">
@@ -14351,12 +14351,12 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t xml:space="preserve">KOLSTRUP BOLIGFORENING</t>
+          <t xml:space="preserve">Aabenraa Kommune</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lergård 104</t>
+          <t xml:space="preserve">Lergård 88</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -14376,20 +14376,20 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">421261, 421262</t>
+          <t xml:space="preserve">311019</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J192">
-        <v>1074</v>
+        <v>815</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311707964</t>
+          <t xml:space="preserve">311717620</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -14399,7 +14399,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-15</t>
+          <t xml:space="preserve">2033-10-25</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -14441,7 +14441,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lergård 88</t>
+          <t xml:space="preserve">Barsøvej 190</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -14451,30 +14451,30 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311019</t>
+          <t xml:space="preserve">8291985</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J193">
-        <v>815</v>
+        <v>98</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311717620</t>
+          <t xml:space="preserve">311750918</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-25</t>
+          <t xml:space="preserve">2034-04-10</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14516,40 +14516,40 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Barsøvej 190</t>
+          <t xml:space="preserve">Funkevej 9A</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">8291985</t>
+          <t xml:space="preserve">5254271</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J194">
-        <v>98</v>
+        <v>415</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311750918</t>
+          <t xml:space="preserve">311763725</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-04-10</t>
+          <t xml:space="preserve">2034-06-03</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14606,15 +14606,15 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J195">
-        <v>415</v>
+        <v>1536</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763725</t>
+          <t xml:space="preserve">311763724</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -14681,15 +14681,15 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J196">
-        <v>1536</v>
+        <v>452</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763724</t>
+          <t xml:space="preserve">311763725</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Funkevej 9A</t>
+          <t xml:space="preserve">Funkevej 9F</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -14756,11 +14756,11 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J197">
-        <v>452</v>
+        <v>200</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
@@ -14816,30 +14816,30 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Funkevej 9F</t>
+          <t xml:space="preserve">Gasværksvej 20</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">5254271</t>
+          <t xml:space="preserve">5775323</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J198">
-        <v>200</v>
+        <v>2574</v>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763725</t>
+          <t xml:space="preserve">311763728</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -14891,7 +14891,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gasværksvej 20</t>
+          <t xml:space="preserve">Gråstenvej 1</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -14901,20 +14901,20 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">5775323</t>
+          <t xml:space="preserve">7747263</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J199">
-        <v>2574</v>
+        <v>2087</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763728</t>
+          <t xml:space="preserve">311763695</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -14966,7 +14966,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gråstenvej 1</t>
+          <t xml:space="preserve">Gråstenvej 12</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -14976,7 +14976,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">7747263</t>
+          <t xml:space="preserve">9303236</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -14985,11 +14985,11 @@
         </is>
       </c>
       <c r="J200">
-        <v>2087</v>
+        <v>677</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763695</t>
+          <t xml:space="preserve">311763696</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -15041,17 +15041,17 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gråstenvej 12</t>
+          <t xml:space="preserve">Grønningen 4</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">9303236</t>
+          <t xml:space="preserve">5255617</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -15060,11 +15060,11 @@
         </is>
       </c>
       <c r="J201">
-        <v>677</v>
+        <v>278</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763696</t>
+          <t xml:space="preserve">311763693</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -15116,35 +15116,35 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønningen 4</t>
+          <t xml:space="preserve">Lavgade 30</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">5255617</t>
+          <t xml:space="preserve">5775595</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J202">
-        <v>278</v>
+        <v>2589</v>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763693</t>
+          <t xml:space="preserve">311763897</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M202" t="inlineStr">
@@ -15191,7 +15191,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lavgade 30</t>
+          <t xml:space="preserve">Nygade 20</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -15206,20 +15206,20 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J203">
-        <v>2589</v>
+        <v>3338</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763897</t>
+          <t xml:space="preserve">311763900</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Total-Tjek</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
@@ -15266,35 +15266,35 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 20</t>
+          <t xml:space="preserve">Strandvej 10</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6340</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">5775595</t>
+          <t xml:space="preserve">5268254</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J204">
-        <v>3338</v>
+        <v>1015</v>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763900</t>
+          <t xml:space="preserve">311763726</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Total-Tjek</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
@@ -15351,20 +15351,20 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">5268254</t>
+          <t xml:space="preserve">5268269</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J205">
-        <v>1015</v>
+        <v>175</v>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763726</t>
+          <t xml:space="preserve">311763735</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -15431,11 +15431,11 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J206">
-        <v>175</v>
+        <v>262</v>
       </c>
       <c r="K206" t="inlineStr">
         <is>
@@ -15506,11 +15506,11 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J207">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="K207" t="inlineStr">
         <is>
@@ -15566,30 +15566,30 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvej 10</t>
+          <t xml:space="preserve">Vestergade 20</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t xml:space="preserve">6340</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">5268269</t>
+          <t xml:space="preserve">5255563</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J208">
-        <v>258</v>
+        <v>868</v>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763735</t>
+          <t xml:space="preserve">311763694</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -15641,7 +15641,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 20</t>
+          <t xml:space="preserve">Østergade 40C</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -15651,20 +15651,20 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">5255563</t>
+          <t xml:space="preserve">5254347</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J209">
-        <v>868</v>
+        <v>520</v>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763694</t>
+          <t xml:space="preserve">311763739</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -15716,7 +15716,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 40C</t>
+          <t xml:space="preserve">Birkholm 7</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -15726,20 +15726,20 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">5254347</t>
+          <t xml:space="preserve">5250365</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J210">
-        <v>520</v>
+        <v>4382</v>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311763739</t>
+          <t xml:space="preserve">311764478</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -15749,7 +15749,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-06-03</t>
+          <t xml:space="preserve">2034-06-06</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15806,11 +15806,11 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J211">
-        <v>4382</v>
+        <v>1154</v>
       </c>
       <c r="K211" t="inlineStr">
         <is>
@@ -15881,15 +15881,15 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J212">
-        <v>1154</v>
+        <v>1483</v>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311764478</t>
+          <t xml:space="preserve">311764476</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -15941,30 +15941,30 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkholm 7</t>
+          <t xml:space="preserve">Dimen 10</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">5250365</t>
+          <t xml:space="preserve">8287001</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J213">
-        <v>1483</v>
+        <v>219</v>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311764476</t>
+          <t xml:space="preserve">311764537</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -16016,17 +16016,17 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dimen 10</t>
+          <t xml:space="preserve">Genner Bygade 3</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">8287001</t>
+          <t xml:space="preserve">8662006</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -16035,11 +16035,11 @@
         </is>
       </c>
       <c r="J214">
-        <v>219</v>
+        <v>1769</v>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311764537</t>
+          <t xml:space="preserve">311764471</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -16106,11 +16106,11 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J215">
-        <v>1769</v>
+        <v>1063</v>
       </c>
       <c r="K215" t="inlineStr">
         <is>
@@ -16181,11 +16181,11 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J216">
-        <v>1063</v>
+        <v>275</v>
       </c>
       <c r="K216" t="inlineStr">
         <is>
@@ -16256,11 +16256,11 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J217">
-        <v>275</v>
+        <v>140</v>
       </c>
       <c r="K217" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Genner Bygade 3</t>
+          <t xml:space="preserve">Hovslundvej 12</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -16326,20 +16326,20 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">8662006</t>
+          <t xml:space="preserve">5247379</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J218">
-        <v>140</v>
+        <v>564</v>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311764471</t>
+          <t xml:space="preserve">311764474</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -16406,11 +16406,11 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J219">
-        <v>564</v>
+        <v>1639</v>
       </c>
       <c r="K219" t="inlineStr">
         <is>
@@ -16466,7 +16466,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovslundvej 12</t>
+          <t xml:space="preserve">Hovslundvej 12A</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -16481,15 +16481,15 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J220">
-        <v>1639</v>
+        <v>237</v>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311764474</t>
+          <t xml:space="preserve">311764473</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -16541,7 +16541,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovslundvej 12A</t>
+          <t xml:space="preserve">Østergade 40B</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -16551,20 +16551,20 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">5247379</t>
+          <t xml:space="preserve">5254347</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J221">
-        <v>237</v>
+        <v>326</v>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311764473</t>
+          <t xml:space="preserve">311764844</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -16574,7 +16574,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-06-06</t>
+          <t xml:space="preserve">2034-06-07</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -16631,11 +16631,11 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J222">
-        <v>326</v>
+        <v>153</v>
       </c>
       <c r="K222" t="inlineStr">
         <is>
@@ -16706,11 +16706,11 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J223">
-        <v>153</v>
+        <v>1272</v>
       </c>
       <c r="K223" t="inlineStr">
         <is>
@@ -16766,30 +16766,30 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 40B</t>
+          <t xml:space="preserve">Bjerggade 3</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t xml:space="preserve">5254347</t>
+          <t xml:space="preserve">5777914</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J224">
-        <v>1272</v>
+        <v>406</v>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t xml:space="preserve">311764844</t>
+          <t xml:space="preserve">311766606</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -16799,7 +16799,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-06-07</t>
+          <t xml:space="preserve">2034-06-14</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16841,7 +16841,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjerggade 3</t>
+          <t xml:space="preserve">Bjerggade 5</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -16851,7 +16851,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t xml:space="preserve">5777914</t>
+          <t xml:space="preserve">5777916</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -16860,11 +16860,11 @@
         </is>
       </c>
       <c r="J225">
-        <v>406</v>
+        <v>232</v>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766606</t>
+          <t xml:space="preserve">311766607</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -16916,7 +16916,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjerggade 5</t>
+          <t xml:space="preserve">Borgmesterløkken 35</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -16926,7 +16926,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t xml:space="preserve">5777916</t>
+          <t xml:space="preserve">7861742</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -16935,11 +16935,11 @@
         </is>
       </c>
       <c r="J226">
-        <v>232</v>
+        <v>340</v>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766607</t>
+          <t xml:space="preserve">311766610</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -16991,7 +16991,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Borgmesterløkken 35</t>
+          <t xml:space="preserve">Haderslevvej 1</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -17001,7 +17001,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t xml:space="preserve">7861742</t>
+          <t xml:space="preserve">5780012</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -17010,11 +17010,11 @@
         </is>
       </c>
       <c r="J227">
-        <v>340</v>
+        <v>1126</v>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766610</t>
+          <t xml:space="preserve">311766629</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -17066,7 +17066,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Haderslevvej 1</t>
+          <t xml:space="preserve">Hjelmalle 3</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
@@ -17076,20 +17076,20 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t xml:space="preserve">5780012</t>
+          <t xml:space="preserve">5777400</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J228">
-        <v>1126</v>
+        <v>2585</v>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766629</t>
+          <t xml:space="preserve">311766632</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -17156,11 +17156,11 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J229">
-        <v>2585</v>
+        <v>1285</v>
       </c>
       <c r="K229" t="inlineStr">
         <is>
@@ -17231,11 +17231,11 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J230">
-        <v>1285</v>
+        <v>5606</v>
       </c>
       <c r="K230" t="inlineStr">
         <is>
@@ -17291,30 +17291,30 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjelmalle 3</t>
+          <t xml:space="preserve">Plantagevej 4</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6330</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">5777400</t>
+          <t xml:space="preserve">5260532</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J231">
-        <v>5606</v>
+        <v>4077</v>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766632</t>
+          <t xml:space="preserve">311766620</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
@@ -17366,30 +17366,30 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plantagevej 4</t>
+          <t xml:space="preserve">Skovbrynet 2</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t xml:space="preserve">6330</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">5260532</t>
+          <t xml:space="preserve">5256718</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J232">
-        <v>4077</v>
+        <v>1396</v>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766620</t>
+          <t xml:space="preserve">311766630</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
@@ -17456,11 +17456,11 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">29</t>
         </is>
       </c>
       <c r="J233">
-        <v>1396</v>
+        <v>1087</v>
       </c>
       <c r="K233" t="inlineStr">
         <is>
@@ -17531,11 +17531,11 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t xml:space="preserve">29</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J234">
-        <v>1087</v>
+        <v>619</v>
       </c>
       <c r="K234" t="inlineStr">
         <is>
@@ -17591,30 +17591,30 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovbrynet 2</t>
+          <t xml:space="preserve">Sønderborgvej 131</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t xml:space="preserve">5256718</t>
+          <t xml:space="preserve">9049653</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J235">
-        <v>619</v>
+        <v>240</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766630</t>
+          <t xml:space="preserve">311766602</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -17666,7 +17666,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderborgvej 131</t>
+          <t xml:space="preserve">Sønderborgvej 133</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -17681,11 +17681,11 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J236">
-        <v>240</v>
+        <v>140</v>
       </c>
       <c r="K236" t="inlineStr">
         <is>
@@ -17741,7 +17741,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderborgvej 133</t>
+          <t xml:space="preserve">Sønderborgvej 135</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -17756,11 +17756,11 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J237">
-        <v>140</v>
+        <v>208</v>
       </c>
       <c r="K237" t="inlineStr">
         <is>
@@ -17816,7 +17816,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderborgvej 135</t>
+          <t xml:space="preserve">Sønderborgvej 137</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -17831,11 +17831,11 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J238">
-        <v>208</v>
+        <v>354</v>
       </c>
       <c r="K238" t="inlineStr">
         <is>
@@ -17891,7 +17891,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderborgvej 137</t>
+          <t xml:space="preserve">Tornhøjvej 18</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -17901,20 +17901,20 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">9049653</t>
+          <t xml:space="preserve">5268090</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J239">
-        <v>354</v>
+        <v>106</v>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766602</t>
+          <t xml:space="preserve">311766631</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
@@ -17966,17 +17966,17 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tornhøjvej 18</t>
+          <t xml:space="preserve">Vestergade 24A</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t xml:space="preserve">5268090</t>
+          <t xml:space="preserve">5255997</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -17985,11 +17985,11 @@
         </is>
       </c>
       <c r="J240">
-        <v>106</v>
+        <v>293</v>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766631</t>
+          <t xml:space="preserve">311766615</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -18041,7 +18041,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 24A</t>
+          <t xml:space="preserve">Østergade 61</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -18051,7 +18051,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve">5255997</t>
+          <t xml:space="preserve">5254851</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -18060,11 +18060,11 @@
         </is>
       </c>
       <c r="J241">
-        <v>293</v>
+        <v>1054</v>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766615</t>
+          <t xml:space="preserve">311766708</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 61</t>
+          <t xml:space="preserve">Østergade 63</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -18131,15 +18131,15 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J242">
-        <v>1054</v>
+        <v>1406</v>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766708</t>
+          <t xml:space="preserve">311766710</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -18191,30 +18191,30 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 63</t>
+          <t xml:space="preserve">Kirkevej 2</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6330</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve">5254851</t>
+          <t xml:space="preserve">5260044</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J243">
-        <v>1406</v>
+        <v>4747</v>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766710</t>
+          <t xml:space="preserve">311766871</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -18224,7 +18224,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-06-14</t>
+          <t xml:space="preserve">2034-06-17</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -18266,7 +18266,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 2</t>
+          <t xml:space="preserve">Padborgvej 55A</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -18281,11 +18281,11 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J244">
-        <v>4747</v>
+        <v>7373</v>
       </c>
       <c r="K244" t="inlineStr">
         <is>
@@ -18341,30 +18341,30 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Padborgvej 55A</t>
+          <t xml:space="preserve">Kallemosen 18</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t xml:space="preserve">6330</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">5260044</t>
+          <t xml:space="preserve">5777160</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J245">
-        <v>7373</v>
+        <v>372</v>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t xml:space="preserve">311766871</t>
+          <t xml:space="preserve">311767653</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -18374,7 +18374,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-06-17</t>
+          <t xml:space="preserve">2034-06-19</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -18416,7 +18416,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kallemosen 18</t>
+          <t xml:space="preserve">Kallemosen 20</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
@@ -18431,11 +18431,11 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J246">
-        <v>372</v>
+        <v>3627</v>
       </c>
       <c r="K246" t="inlineStr">
         <is>
@@ -18506,15 +18506,15 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J247">
-        <v>3627</v>
+        <v>191</v>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t xml:space="preserve">311767653</t>
+          <t xml:space="preserve">311767649</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
@@ -18566,30 +18566,30 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kallemosen 20</t>
+          <t xml:space="preserve">Padborgvej 55A</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6330</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">5777160</t>
+          <t xml:space="preserve">5260044</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J248">
-        <v>191</v>
+        <v>243</v>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t xml:space="preserve">311767649</t>
+          <t xml:space="preserve">311767646</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
@@ -18641,30 +18641,30 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Padborgvej 55A</t>
+          <t xml:space="preserve">Skovbrynet 10</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t xml:space="preserve">6330</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">5260044</t>
+          <t xml:space="preserve">5256718</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J249">
-        <v>243</v>
+        <v>2110</v>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t xml:space="preserve">311767646</t>
+          <t xml:space="preserve">311767974</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
@@ -18674,7 +18674,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-06-19</t>
+          <t xml:space="preserve">2034-06-20</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -18731,15 +18731,15 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J250">
-        <v>2110</v>
+        <v>470</v>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t xml:space="preserve">311767974</t>
+          <t xml:space="preserve">311767973</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
@@ -18791,7 +18791,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovbrynet 10</t>
+          <t xml:space="preserve">Skovbrynet 4</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -18806,15 +18806,15 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J251">
-        <v>470</v>
+        <v>404</v>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t xml:space="preserve">311767973</t>
+          <t xml:space="preserve">311767976</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
@@ -18866,30 +18866,30 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovbrynet 4</t>
+          <t xml:space="preserve">Pilemosen 21</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">5256718</t>
+          <t xml:space="preserve">5777457</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J252">
-        <v>404</v>
+        <v>1635</v>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t xml:space="preserve">311767976</t>
+          <t xml:space="preserve">311768984</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
@@ -18899,7 +18899,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-06-20</t>
+          <t xml:space="preserve">2034-06-25</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18941,7 +18941,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pilemosen 21</t>
+          <t xml:space="preserve">Sønderborgvej 137</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -18951,20 +18951,20 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">5777457</t>
+          <t xml:space="preserve">9049653</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J253">
-        <v>1635</v>
+        <v>542</v>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t xml:space="preserve">311768984</t>
+          <t xml:space="preserve">311770633</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
@@ -18974,7 +18974,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-06-25</t>
+          <t xml:space="preserve">2034-07-02</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -19031,15 +19031,15 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J254">
-        <v>542</v>
+        <v>6116</v>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t xml:space="preserve">311770633</t>
+          <t xml:space="preserve">311770634</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
@@ -19106,11 +19106,11 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J255">
-        <v>6116</v>
+        <v>664</v>
       </c>
       <c r="K255" t="inlineStr">
         <is>
@@ -19166,30 +19166,30 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderborgvej 137</t>
+          <t xml:space="preserve">Slogsherredsvej 41</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6372</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t xml:space="preserve">9049653</t>
+          <t xml:space="preserve">737562, 5238011</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J256">
-        <v>664</v>
+        <v>1394</v>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t xml:space="preserve">311770634</t>
+          <t xml:space="preserve">311772649</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
@@ -19199,7 +19199,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-07-02</t>
+          <t xml:space="preserve">2034-07-10</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -19256,15 +19256,15 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J257">
-        <v>1394</v>
+        <v>1287</v>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t xml:space="preserve">311772649</t>
+          <t xml:space="preserve">311772650</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
@@ -19316,30 +19316,30 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Slogsherredsvej 41</t>
+          <t xml:space="preserve">Møllemærsk 24</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t xml:space="preserve">6372</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">737562, 5238011</t>
+          <t xml:space="preserve">309127</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J258">
-        <v>1287</v>
+        <v>240</v>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t xml:space="preserve">311772650</t>
+          <t xml:space="preserve">311783172</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
@@ -19349,7 +19349,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-07-10</t>
+          <t xml:space="preserve">2034-09-06</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -19406,7 +19406,7 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J259">
@@ -19476,16 +19476,16 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">309127</t>
+          <t xml:space="preserve">309127, 309128, 309129</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J260">
-        <v>240</v>
+        <v>5924</v>
       </c>
       <c r="K260" t="inlineStr">
         <is>
@@ -19541,40 +19541,40 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllemærsk 24</t>
+          <t xml:space="preserve">Vestergade 14</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">309127, 309128, 309129</t>
+          <t xml:space="preserve">5255302</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J261">
-        <v>5924</v>
+        <v>4677</v>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t xml:space="preserve">311783172</t>
+          <t xml:space="preserve">311792061</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-09-06</t>
+          <t xml:space="preserve">2034-10-17</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -19616,40 +19616,40 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 14</t>
+          <t xml:space="preserve">Bag Møllen 3</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">5255302</t>
+          <t xml:space="preserve">5777123</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J262">
-        <v>4677</v>
+        <v>170</v>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t xml:space="preserve">311792061</t>
+          <t xml:space="preserve">311813582</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-17</t>
+          <t xml:space="preserve">2035-02-24</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -19691,7 +19691,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bag Møllen 3</t>
+          <t xml:space="preserve">Bag Møllen 5</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
@@ -19706,7 +19706,7 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J263">
@@ -19766,7 +19766,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bag Møllen 5</t>
+          <t xml:space="preserve">Kirkeplads 3A</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
@@ -19776,20 +19776,20 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">5777123</t>
+          <t xml:space="preserve">5774705</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J264">
-        <v>170</v>
+        <v>408</v>
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813582</t>
+          <t xml:space="preserve">311813570</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
@@ -19841,7 +19841,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkeplads 3A</t>
+          <t xml:space="preserve">Kirkeplads 9</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
@@ -19851,7 +19851,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t xml:space="preserve">5774705</t>
+          <t xml:space="preserve">5774683</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -19860,11 +19860,11 @@
         </is>
       </c>
       <c r="J265">
-        <v>408</v>
+        <v>111</v>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813570</t>
+          <t xml:space="preserve">311813571</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
@@ -19916,7 +19916,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkeplads 9</t>
+          <t xml:space="preserve">Kirketoften 10</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
@@ -19926,7 +19926,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">5774683</t>
+          <t xml:space="preserve">5252364</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -19935,11 +19935,11 @@
         </is>
       </c>
       <c r="J266">
-        <v>111</v>
+        <v>325</v>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813571</t>
+          <t xml:space="preserve">311813574</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
@@ -19991,7 +19991,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirketoften 10</t>
+          <t xml:space="preserve">Kirketoften 20</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
@@ -20006,7 +20006,7 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J267">
@@ -20066,7 +20066,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirketoften 20</t>
+          <t xml:space="preserve">Kirketoften 30</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
@@ -20081,7 +20081,7 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J268">
@@ -20141,7 +20141,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirketoften 30</t>
+          <t xml:space="preserve">Kirketoften 40</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
@@ -20156,15 +20156,15 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J269">
-        <v>325</v>
+        <v>360</v>
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813574</t>
+          <t xml:space="preserve">311813682</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
@@ -20216,7 +20216,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirketoften 40</t>
+          <t xml:space="preserve">Kirketoften 50</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
@@ -20231,7 +20231,7 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J270">
@@ -20291,7 +20291,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirketoften 50</t>
+          <t xml:space="preserve">Kirketoften 60</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
@@ -20306,20 +20306,20 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J271">
-        <v>360</v>
+        <v>1635</v>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813682</t>
+          <t xml:space="preserve">311813683</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M271" t="inlineStr">
@@ -20366,7 +20366,7 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirketoften 60</t>
+          <t xml:space="preserve">Langebro 18</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
@@ -20376,25 +20376,25 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">5252364</t>
+          <t xml:space="preserve">5777123</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J272">
-        <v>1635</v>
+        <v>170</v>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813683</t>
+          <t xml:space="preserve">311813582</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
@@ -20441,7 +20441,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langebro 18</t>
+          <t xml:space="preserve">Rådhusgang 4</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
@@ -20451,20 +20451,20 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">5777123</t>
+          <t xml:space="preserve">5775091</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J273">
-        <v>170</v>
+        <v>1235</v>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813582</t>
+          <t xml:space="preserve">311813583</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -20516,7 +20516,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusgang 4</t>
+          <t xml:space="preserve">Klinkbjerg 34</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
@@ -20526,7 +20526,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve">5775091</t>
+          <t xml:space="preserve">5777878</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -20535,11 +20535,11 @@
         </is>
       </c>
       <c r="J274">
-        <v>1235</v>
+        <v>308</v>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813583</t>
+          <t xml:space="preserve">311813806</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -20549,7 +20549,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-02-24</t>
+          <t xml:space="preserve">2035-02-25</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -20591,7 +20591,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klinkbjerg 34</t>
+          <t xml:space="preserve">Langrode 11</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
@@ -20601,7 +20601,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">5777878</t>
+          <t xml:space="preserve">5777949</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -20610,11 +20610,11 @@
         </is>
       </c>
       <c r="J275">
-        <v>308</v>
+        <v>3254</v>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813806</t>
+          <t xml:space="preserve">311813816</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -20666,7 +20666,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langrode 11</t>
+          <t xml:space="preserve">Langrode 13A</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
@@ -20681,15 +20681,15 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J276">
-        <v>3254</v>
+        <v>171</v>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813816</t>
+          <t xml:space="preserve">311813853</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
@@ -20741,7 +20741,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langrode 13A</t>
+          <t xml:space="preserve">Langrode 13D</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
@@ -20756,11 +20756,11 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J277">
-        <v>171</v>
+        <v>228</v>
       </c>
       <c r="K277" t="inlineStr">
         <is>
@@ -20816,7 +20816,7 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langrode 13D</t>
+          <t xml:space="preserve">Langrode 13H</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
@@ -20831,11 +20831,11 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J278">
-        <v>228</v>
+        <v>171</v>
       </c>
       <c r="K278" t="inlineStr">
         <is>
@@ -20891,7 +20891,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langrode 13H</t>
+          <t xml:space="preserve">Langrode 15A</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
@@ -20906,7 +20906,7 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J279">
@@ -20966,7 +20966,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langrode 15A</t>
+          <t xml:space="preserve">Langrode 15D</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
@@ -20981,11 +20981,11 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J280">
-        <v>171</v>
+        <v>228</v>
       </c>
       <c r="K280" t="inlineStr">
         <is>
@@ -21041,7 +21041,7 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langrode 15D</t>
+          <t xml:space="preserve">Langrode 15H</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
@@ -21056,15 +21056,15 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J281">
-        <v>228</v>
+        <v>171</v>
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813853</t>
+          <t xml:space="preserve">311813855</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
@@ -21116,7 +21116,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langrode 15H</t>
+          <t xml:space="preserve">Langrode 7A</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
@@ -21131,15 +21131,15 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J282">
-        <v>171</v>
+        <v>640</v>
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813855</t>
+          <t xml:space="preserve">311813818</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
@@ -21191,7 +21191,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langrode 7A</t>
+          <t xml:space="preserve">Langrode 9A</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
@@ -21206,7 +21206,7 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="J283">
@@ -21266,40 +21266,40 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langrode 9A</t>
+          <t xml:space="preserve">Harkærvej 13</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6340</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t xml:space="preserve">5777949</t>
+          <t xml:space="preserve">737434, 1808354</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J284">
-        <v>640</v>
+        <v>1934</v>
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t xml:space="preserve">311813818</t>
+          <t xml:space="preserve">311814773</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">OBH</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-02-25</t>
+          <t xml:space="preserve">2035-02-28</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -21356,11 +21356,11 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J285">
-        <v>1934</v>
+        <v>1343</v>
       </c>
       <c r="K285" t="inlineStr">
         <is>
@@ -21431,11 +21431,11 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J286">
-        <v>1343</v>
+        <v>3168</v>
       </c>
       <c r="K286" t="inlineStr">
         <is>
@@ -21506,15 +21506,15 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J287">
-        <v>3168</v>
+        <v>895</v>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814773</t>
+          <t xml:space="preserve">311814770</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
@@ -21581,15 +21581,15 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J288">
-        <v>895</v>
+        <v>191</v>
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814770</t>
+          <t xml:space="preserve">311814771</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
@@ -21641,30 +21641,30 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t xml:space="preserve">Harkærvej 13</t>
+          <t xml:space="preserve">Sønderborgvej 129</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t xml:space="preserve">6340</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t xml:space="preserve">737434, 1808354</t>
+          <t xml:space="preserve">737489, 9049653</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="J289">
-        <v>191</v>
+        <v>1674</v>
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t xml:space="preserve">311814771</t>
+          <t xml:space="preserve">311817074</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
@@ -21674,7 +21674,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-02-28</t>
+          <t xml:space="preserve">2035-03-12</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -21716,7 +21716,7 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderborgvej 129</t>
+          <t xml:space="preserve">Løjt Skolegade 27</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
@@ -21726,30 +21726,30 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t xml:space="preserve">737489, 9049653</t>
+          <t xml:space="preserve">5253360</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J290">
-        <v>1674</v>
+        <v>858</v>
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t xml:space="preserve">311817074</t>
+          <t xml:space="preserve">311821040</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-12</t>
+          <t xml:space="preserve">2035-03-28</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -21791,7 +21791,7 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Løjt Skolegade 27</t>
+          <t xml:space="preserve">Løjt Skolegade 27A</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
@@ -21806,11 +21806,11 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J291">
-        <v>858</v>
+        <v>256</v>
       </c>
       <c r="K291" t="inlineStr">
         <is>
@@ -21866,7 +21866,7 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Løjt Skolegade 27A</t>
+          <t xml:space="preserve">Nyløkke 17</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
@@ -21876,20 +21876,20 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t xml:space="preserve">5253360</t>
+          <t xml:space="preserve">5780157</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J292">
-        <v>256</v>
+        <v>280</v>
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821040</t>
+          <t xml:space="preserve">311821028</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
@@ -21941,7 +21941,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyløkke 17</t>
+          <t xml:space="preserve">Stubbæk Skolegade 1</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
@@ -21951,20 +21951,20 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t xml:space="preserve">5780157</t>
+          <t xml:space="preserve">5265175</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J293">
-        <v>280</v>
+        <v>373</v>
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821028</t>
+          <t xml:space="preserve">311821030</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
@@ -22016,7 +22016,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stubbæk Skolegade 1</t>
+          <t xml:space="preserve">Søstvej 11</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
@@ -22026,20 +22026,20 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t xml:space="preserve">5265175</t>
+          <t xml:space="preserve">5779435</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J294">
-        <v>373</v>
+        <v>624</v>
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821030</t>
+          <t xml:space="preserve">311821027</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
@@ -22091,7 +22091,7 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søstvej 11</t>
+          <t xml:space="preserve">Lille Kolstrup 10</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
@@ -22101,7 +22101,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t xml:space="preserve">5779435</t>
+          <t xml:space="preserve">5779275</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -22110,11 +22110,11 @@
         </is>
       </c>
       <c r="J295">
-        <v>624</v>
+        <v>2117</v>
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t xml:space="preserve">311821027</t>
+          <t xml:space="preserve">311831284</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
@@ -22124,7 +22124,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-03-28</t>
+          <t xml:space="preserve">2035-05-13</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -22166,7 +22166,7 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lille Kolstrup 10</t>
+          <t xml:space="preserve">Lille Pottergade 8A</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
@@ -22176,7 +22176,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t xml:space="preserve">5779275</t>
+          <t xml:space="preserve">5774735</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -22185,11 +22185,11 @@
         </is>
       </c>
       <c r="J296">
-        <v>2117</v>
+        <v>242</v>
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831284</t>
+          <t xml:space="preserve">311831285</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
@@ -22241,7 +22241,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lille Pottergade 8A</t>
+          <t xml:space="preserve">Nygade 21</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
@@ -22251,20 +22251,20 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t xml:space="preserve">5774735</t>
+          <t xml:space="preserve">5774474</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J297">
-        <v>242</v>
+        <v>1330</v>
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831285</t>
+          <t xml:space="preserve">311831290</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
@@ -22316,7 +22316,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 21</t>
+          <t xml:space="preserve">Nygade 23A</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
@@ -22331,15 +22331,15 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J298">
-        <v>1330</v>
+        <v>2030</v>
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831290</t>
+          <t xml:space="preserve">311831286</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
@@ -22391,7 +22391,7 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 23A</t>
+          <t xml:space="preserve">Nygade 23C</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
@@ -22406,15 +22406,15 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J299">
-        <v>2030</v>
+        <v>1623</v>
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831286</t>
+          <t xml:space="preserve">311831291</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
@@ -22466,7 +22466,7 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 23C</t>
+          <t xml:space="preserve">Nygade 23D</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
@@ -22481,15 +22481,15 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J300">
-        <v>1623</v>
+        <v>1076</v>
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831291</t>
+          <t xml:space="preserve">311831292</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
@@ -22541,7 +22541,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 23D</t>
+          <t xml:space="preserve">Nyløkke 4</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
@@ -22551,20 +22551,20 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t xml:space="preserve">5774474</t>
+          <t xml:space="preserve">8540377</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J301">
-        <v>1076</v>
+        <v>9062</v>
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831292</t>
+          <t xml:space="preserve">311831238</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
@@ -22616,7 +22616,7 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyløkke 4</t>
+          <t xml:space="preserve">Stubbæk Bygade 1</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
@@ -22626,20 +22626,20 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t xml:space="preserve">8540377</t>
+          <t xml:space="preserve">5265560</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J302">
-        <v>9062</v>
+        <v>790</v>
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831238</t>
+          <t xml:space="preserve">311831239</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
@@ -22691,7 +22691,7 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stubbæk Bygade 1</t>
+          <t xml:space="preserve">Stubbæk Skolegade 8</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
@@ -22701,7 +22701,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t xml:space="preserve">5265560</t>
+          <t xml:space="preserve">5265545</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -22710,11 +22710,11 @@
         </is>
       </c>
       <c r="J303">
-        <v>790</v>
+        <v>666</v>
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831239</t>
+          <t xml:space="preserve">311831237</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
@@ -22766,7 +22766,7 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stubbæk Skolegade 8</t>
+          <t xml:space="preserve">Tøndervej 90</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
@@ -22776,7 +22776,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t xml:space="preserve">5265545</t>
+          <t xml:space="preserve">5776547</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -22785,11 +22785,11 @@
         </is>
       </c>
       <c r="J304">
-        <v>666</v>
+        <v>2511</v>
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831237</t>
+          <t xml:space="preserve">311831283</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
@@ -22856,11 +22856,11 @@
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J305">
-        <v>2511</v>
+        <v>4724</v>
       </c>
       <c r="K305" t="inlineStr">
         <is>
@@ -22931,11 +22931,11 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J306">
-        <v>4724</v>
+        <v>490</v>
       </c>
       <c r="K306" t="inlineStr">
         <is>
@@ -23006,11 +23006,11 @@
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J307">
-        <v>490</v>
+        <v>2476</v>
       </c>
       <c r="K307" t="inlineStr">
         <is>
@@ -23066,7 +23066,7 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tøndervej 90</t>
+          <t xml:space="preserve">Tøndervej 92</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
@@ -23081,15 +23081,15 @@
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J308">
-        <v>2476</v>
+        <v>762</v>
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831283</t>
+          <t xml:space="preserve">311831294</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
@@ -23141,7 +23141,7 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tøndervej 92</t>
+          <t xml:space="preserve">Løjt Skolegade 14</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
@@ -23151,20 +23151,20 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t xml:space="preserve">5776547</t>
+          <t xml:space="preserve">5252489</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J309">
-        <v>762</v>
+        <v>984</v>
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831294</t>
+          <t xml:space="preserve">311831852</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
@@ -23174,7 +23174,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-13</t>
+          <t xml:space="preserve">2035-05-14</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -23231,11 +23231,11 @@
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J310">
-        <v>984</v>
+        <v>1460</v>
       </c>
       <c r="K310" t="inlineStr">
         <is>
@@ -23306,11 +23306,11 @@
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J311">
-        <v>1460</v>
+        <v>1034</v>
       </c>
       <c r="K311" t="inlineStr">
         <is>
@@ -23381,11 +23381,11 @@
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J312">
-        <v>1034</v>
+        <v>5105</v>
       </c>
       <c r="K312" t="inlineStr">
         <is>
@@ -23441,7 +23441,7 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Løjt Skolegade 14</t>
+          <t xml:space="preserve">Dronning Margrethes Vej 60</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
@@ -23451,20 +23451,20 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t xml:space="preserve">5252489</t>
+          <t xml:space="preserve">5775088</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J313">
-        <v>5105</v>
+        <v>2142</v>
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t xml:space="preserve">311831852</t>
+          <t xml:space="preserve">311832051</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
@@ -23474,7 +23474,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-14</t>
+          <t xml:space="preserve">2035-05-15</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -23531,11 +23531,11 @@
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J314">
-        <v>2142</v>
+        <v>1062</v>
       </c>
       <c r="K314" t="inlineStr">
         <is>
@@ -23606,11 +23606,11 @@
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J315">
-        <v>1062</v>
+        <v>2149</v>
       </c>
       <c r="K315" t="inlineStr">
         <is>
@@ -23666,7 +23666,7 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronning Margrethes Vej 60</t>
+          <t xml:space="preserve">Bjerggade 4E</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
@@ -23676,20 +23676,20 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t xml:space="preserve">5775088</t>
+          <t xml:space="preserve">9058289</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J316">
-        <v>2149</v>
+        <v>610</v>
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t xml:space="preserve">311832051</t>
+          <t xml:space="preserve">311848623</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
@@ -23699,7 +23699,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-05-15</t>
+          <t xml:space="preserve">2035-08-12</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -23741,7 +23741,7 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjerggade 4E</t>
+          <t xml:space="preserve">Bjerggade 4F</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
@@ -23756,15 +23756,15 @@
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J317">
-        <v>610</v>
+        <v>1113</v>
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t xml:space="preserve">311848623</t>
+          <t xml:space="preserve">311848622</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
@@ -23816,7 +23816,7 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjerggade 4F</t>
+          <t xml:space="preserve">Bjerggade 4G</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
@@ -23831,15 +23831,15 @@
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J318">
-        <v>1113</v>
+        <v>604</v>
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t xml:space="preserve">311848622</t>
+          <t xml:space="preserve">311848621</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
@@ -23891,7 +23891,7 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjerggade 4G</t>
+          <t xml:space="preserve">Bjerggade 4Q</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
@@ -23906,15 +23906,15 @@
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J319">
-        <v>604</v>
+        <v>120</v>
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t xml:space="preserve">311848621</t>
+          <t xml:space="preserve">311868873</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
@@ -23924,7 +23924,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-12</t>
+          <t xml:space="preserve">2035-11-18</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -23966,7 +23966,7 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjerggade 4Q</t>
+          <t xml:space="preserve">Bjerggade 8</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
@@ -23976,7 +23976,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t xml:space="preserve">9058289</t>
+          <t xml:space="preserve">10202622</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -23985,11 +23985,11 @@
         </is>
       </c>
       <c r="J320">
-        <v>120</v>
+        <v>427</v>
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868873</t>
+          <t xml:space="preserve">311868888</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
@@ -24041,7 +24041,7 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjerggade 8</t>
+          <t xml:space="preserve">Lille Kolstrup 12</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
@@ -24051,20 +24051,20 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t xml:space="preserve">10202622</t>
+          <t xml:space="preserve">5779275</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J321">
-        <v>427</v>
+        <v>132</v>
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868888</t>
+          <t xml:space="preserve">311868870</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
@@ -24116,30 +24116,30 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lille Kolstrup 12</t>
+          <t xml:space="preserve">Nørremarken 44A</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6360</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t xml:space="preserve">5779275</t>
+          <t xml:space="preserve">5243868</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J322">
-        <v>132</v>
+        <v>1263</v>
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868870</t>
+          <t xml:space="preserve">311868866</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
@@ -24191,7 +24191,7 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørremarken 44A</t>
+          <t xml:space="preserve">Nørremarken 44C</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
@@ -24201,20 +24201,20 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t xml:space="preserve">5243868</t>
+          <t xml:space="preserve">5242501</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J323">
-        <v>1263</v>
+        <v>1921</v>
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868866</t>
+          <t xml:space="preserve">311868868</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
@@ -24266,30 +24266,30 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørremarken 44C</t>
+          <t xml:space="preserve">Skolegade 10</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t xml:space="preserve">6360</t>
+          <t xml:space="preserve">6230</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t xml:space="preserve">5242501</t>
+          <t xml:space="preserve">5245639</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J324">
-        <v>1921</v>
+        <v>285</v>
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868868</t>
+          <t xml:space="preserve">311868879</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
@@ -24341,7 +24341,7 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 10</t>
+          <t xml:space="preserve">Skolegade 8</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
@@ -24356,15 +24356,15 @@
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J325">
-        <v>285</v>
+        <v>805</v>
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868879</t>
+          <t xml:space="preserve">311868878</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
@@ -24431,11 +24431,11 @@
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J326">
-        <v>805</v>
+        <v>650</v>
       </c>
       <c r="K326" t="inlineStr">
         <is>
@@ -24506,11 +24506,11 @@
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J327">
-        <v>650</v>
+        <v>71</v>
       </c>
       <c r="K327" t="inlineStr">
         <is>
@@ -24581,11 +24581,11 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J328">
-        <v>71</v>
+        <v>454</v>
       </c>
       <c r="K328" t="inlineStr">
         <is>
@@ -24656,11 +24656,11 @@
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J329">
-        <v>454</v>
+        <v>116</v>
       </c>
       <c r="K329" t="inlineStr">
         <is>
@@ -24716,30 +24716,30 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 8</t>
+          <t xml:space="preserve">Skolevænget 33</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t xml:space="preserve">6230</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t xml:space="preserve">5245639</t>
+          <t xml:space="preserve">100006578</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J330">
-        <v>116</v>
+        <v>1429</v>
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868878</t>
+          <t xml:space="preserve">311868875</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
@@ -24806,15 +24806,15 @@
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J331">
-        <v>1429</v>
+        <v>860</v>
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868875</t>
+          <t xml:space="preserve">311868877</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
@@ -24866,7 +24866,7 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevænget 33</t>
+          <t xml:space="preserve">Ved Slottet 20</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
@@ -24876,20 +24876,20 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t xml:space="preserve">100006578</t>
+          <t xml:space="preserve">5774977</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J332">
-        <v>860</v>
+        <v>170</v>
       </c>
       <c r="K332" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868877</t>
+          <t xml:space="preserve">311868863</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
@@ -24941,7 +24941,7 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Slottet 20</t>
+          <t xml:space="preserve">Ved Slottet 24</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
@@ -24956,15 +24956,15 @@
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J333">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="K333" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868863</t>
+          <t xml:space="preserve">311868864</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
@@ -25016,7 +25016,7 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Slottet 24</t>
+          <t xml:space="preserve">Ved Slottet 28</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
@@ -25026,12 +25026,12 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t xml:space="preserve">5774977</t>
+          <t xml:space="preserve">5777554</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J334">
@@ -25039,7 +25039,7 @@
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868864</t>
+          <t xml:space="preserve">311868865</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">
@@ -25091,17 +25091,17 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ved Slottet 28</t>
+          <t xml:space="preserve">Højskolevej 1</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6360</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t xml:space="preserve">5777554</t>
+          <t xml:space="preserve">5243526</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -25110,11 +25110,11 @@
         </is>
       </c>
       <c r="J335">
-        <v>168</v>
+        <v>544</v>
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868865</t>
+          <t xml:space="preserve">311871854</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
@@ -25124,7 +25124,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-18</t>
+          <t xml:space="preserve">2035-12-04</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -25166,7 +25166,7 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højskolevej 1</t>
+          <t xml:space="preserve">Højskolevej 3</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
@@ -25176,7 +25176,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t xml:space="preserve">5243526</t>
+          <t xml:space="preserve">5243450</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -25185,11 +25185,11 @@
         </is>
       </c>
       <c r="J336">
-        <v>544</v>
+        <v>182</v>
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871854</t>
+          <t xml:space="preserve">311872102</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
@@ -25199,7 +25199,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-04</t>
+          <t xml:space="preserve">2035-12-05</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -25241,30 +25241,30 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højskolevej 3</t>
+          <t xml:space="preserve">Bjerggade 4C</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t xml:space="preserve">6360</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t xml:space="preserve">5243450</t>
+          <t xml:space="preserve">9058289</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J337">
-        <v>182</v>
+        <v>891</v>
       </c>
       <c r="K337" t="inlineStr">
         <is>
-          <t xml:space="preserve">311872102</t>
+          <t xml:space="preserve">311875341</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
@@ -25274,7 +25274,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-05</t>
+          <t xml:space="preserve">2036-01-06</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -25316,7 +25316,7 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjerggade 4C</t>
+          <t xml:space="preserve">Bladknæk 51</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
@@ -25326,20 +25326,20 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t xml:space="preserve">9058289</t>
+          <t xml:space="preserve">8114886</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J338">
-        <v>891</v>
+        <v>944</v>
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875341</t>
+          <t xml:space="preserve">311875347</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
@@ -25391,7 +25391,7 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bladknæk 51</t>
+          <t xml:space="preserve">Byvænget 4</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
@@ -25401,7 +25401,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t xml:space="preserve">8114886</t>
+          <t xml:space="preserve">8052209</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -25410,11 +25410,11 @@
         </is>
       </c>
       <c r="J339">
-        <v>944</v>
+        <v>352</v>
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875347</t>
+          <t xml:space="preserve">311875338</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
@@ -25466,7 +25466,7 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byvænget 4</t>
+          <t xml:space="preserve">Fjordløkke 1</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
@@ -25476,7 +25476,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t xml:space="preserve">8052209</t>
+          <t xml:space="preserve">5777609</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -25485,11 +25485,11 @@
         </is>
       </c>
       <c r="J340">
-        <v>352</v>
+        <v>540</v>
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875338</t>
+          <t xml:space="preserve">311875336</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
@@ -25541,7 +25541,7 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fjordløkke 1</t>
+          <t xml:space="preserve">Gråstenvej 3B</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
@@ -25551,7 +25551,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t xml:space="preserve">5777609</t>
+          <t xml:space="preserve">7747264</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -25560,11 +25560,11 @@
         </is>
       </c>
       <c r="J341">
-        <v>540</v>
+        <v>212</v>
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875336</t>
+          <t xml:space="preserve">311875349</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
@@ -25616,7 +25616,7 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gråstenvej 3B</t>
+          <t xml:space="preserve">Langebro 22</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
@@ -25626,7 +25626,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t xml:space="preserve">7747264</t>
+          <t xml:space="preserve">5776990</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -25635,11 +25635,11 @@
         </is>
       </c>
       <c r="J342">
-        <v>212</v>
+        <v>592</v>
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875349</t>
+          <t xml:space="preserve">311875353</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
@@ -25691,7 +25691,7 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langebro 22</t>
+          <t xml:space="preserve">Lergård 2</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
@@ -25701,7 +25701,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t xml:space="preserve">5776990</t>
+          <t xml:space="preserve">7681750</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -25710,11 +25710,11 @@
         </is>
       </c>
       <c r="J343">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="K343" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875353</t>
+          <t xml:space="preserve">311875339</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
@@ -25766,7 +25766,7 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lergård 2</t>
+          <t xml:space="preserve">Nygade 46</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
@@ -25776,7 +25776,7 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t xml:space="preserve">7681750</t>
+          <t xml:space="preserve">7791737</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -25785,11 +25785,11 @@
         </is>
       </c>
       <c r="J344">
-        <v>589</v>
+        <v>556</v>
       </c>
       <c r="K344" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875339</t>
+          <t xml:space="preserve">311875342</t>
         </is>
       </c>
       <c r="L344" t="inlineStr">
@@ -25841,7 +25841,7 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nygade 46</t>
+          <t xml:space="preserve">Nyløkke 2</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
@@ -25851,20 +25851,20 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t xml:space="preserve">7791737</t>
+          <t xml:space="preserve">8540377</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J345">
-        <v>556</v>
+        <v>3204</v>
       </c>
       <c r="K345" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875342</t>
+          <t xml:space="preserve">311875333</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
@@ -25916,7 +25916,7 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyløkke 2</t>
+          <t xml:space="preserve">Posekærvej 20</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
@@ -25926,20 +25926,20 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t xml:space="preserve">8540377</t>
+          <t xml:space="preserve">5776859</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J346">
-        <v>3204</v>
+        <v>1615</v>
       </c>
       <c r="K346" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875333</t>
+          <t xml:space="preserve">311875334</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
@@ -25991,7 +25991,7 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t xml:space="preserve">Posekærvej 20</t>
+          <t xml:space="preserve">Præsteskoven 40</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
@@ -26001,20 +26001,20 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t xml:space="preserve">5776859</t>
+          <t xml:space="preserve">9392994</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J347">
-        <v>1615</v>
+        <v>690</v>
       </c>
       <c r="K347" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875334</t>
+          <t xml:space="preserve">311875343</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
@@ -26066,7 +26066,7 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t xml:space="preserve">Præsteskoven 40</t>
+          <t xml:space="preserve">Sejsbjerg 16</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
@@ -26076,20 +26076,20 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t xml:space="preserve">9392994</t>
+          <t xml:space="preserve">8353545</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J348">
-        <v>690</v>
+        <v>741</v>
       </c>
       <c r="K348" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875343</t>
+          <t xml:space="preserve">311875345</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
@@ -26141,7 +26141,7 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sejsbjerg 16</t>
+          <t xml:space="preserve">Stubbæk Vestergade 24</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
@@ -26151,7 +26151,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t xml:space="preserve">8353545</t>
+          <t xml:space="preserve">5265034</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -26160,11 +26160,11 @@
         </is>
       </c>
       <c r="J349">
-        <v>741</v>
+        <v>80</v>
       </c>
       <c r="K349" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875345</t>
+          <t xml:space="preserve">311875354</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
@@ -26216,7 +26216,7 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stubbæk Vestergade 24</t>
+          <t xml:space="preserve">Vestvejen 25</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
@@ -26226,20 +26226,20 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t xml:space="preserve">5265034</t>
+          <t xml:space="preserve">5776345</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J350">
-        <v>80</v>
+        <v>1081</v>
       </c>
       <c r="K350" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875354</t>
+          <t xml:space="preserve">311875335</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
@@ -26306,11 +26306,11 @@
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J351">
-        <v>1081</v>
+        <v>145</v>
       </c>
       <c r="K351" t="inlineStr">
         <is>
@@ -26366,30 +26366,30 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestvejen 25</t>
+          <t xml:space="preserve">Åbjerg 8B</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200</t>
+          <t xml:space="preserve">6340</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t xml:space="preserve">5776345</t>
+          <t xml:space="preserve">5263733</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J352">
-        <v>145</v>
+        <v>853</v>
       </c>
       <c r="K352" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875335</t>
+          <t xml:space="preserve">311875352</t>
         </is>
       </c>
       <c r="L352" t="inlineStr">
@@ -26456,11 +26456,11 @@
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J353">
-        <v>853</v>
+        <v>1115</v>
       </c>
       <c r="K353" t="inlineStr">
         <is>
@@ -26531,11 +26531,11 @@
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J354">
-        <v>1115</v>
+        <v>381</v>
       </c>
       <c r="K354" t="inlineStr">
         <is>
@@ -26606,11 +26606,11 @@
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J355">
-        <v>381</v>
+        <v>445</v>
       </c>
       <c r="K355" t="inlineStr">
         <is>
@@ -26681,11 +26681,11 @@
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J356">
-        <v>445</v>
+        <v>925</v>
       </c>
       <c r="K356" t="inlineStr">
         <is>
@@ -26756,11 +26756,11 @@
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J357">
-        <v>925</v>
+        <v>405</v>
       </c>
       <c r="K357" t="inlineStr">
         <is>
@@ -26831,11 +26831,11 @@
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J358">
-        <v>405</v>
+        <v>2453</v>
       </c>
       <c r="K358" t="inlineStr">
         <is>
@@ -26891,30 +26891,30 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t xml:space="preserve">Åbjerg 8B</t>
+          <t xml:space="preserve">Nyløkke 2</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t xml:space="preserve">6340</t>
+          <t xml:space="preserve">6200</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t xml:space="preserve">5263733</t>
+          <t xml:space="preserve">8540377</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="J359">
-        <v>2453</v>
+        <v>85</v>
       </c>
       <c r="K359" t="inlineStr">
         <is>
-          <t xml:space="preserve">311875352</t>
+          <t xml:space="preserve">311885684</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
@@ -26924,7 +26924,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-01-06</t>
+          <t xml:space="preserve">2036-03-05</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -26966,7 +26966,7 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyløkke 2</t>
+          <t xml:space="preserve">Sandved 45</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
@@ -26976,30 +26976,30 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t xml:space="preserve">8540377</t>
+          <t xml:space="preserve">5777338</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J360">
-        <v>85</v>
+        <v>1700</v>
       </c>
       <c r="K360" t="inlineStr">
         <is>
-          <t xml:space="preserve">311885684</t>
+          <t xml:space="preserve">311886895</t>
         </is>
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Ingeniørgruppen Haderslev ApS</t>
         </is>
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-05</t>
+          <t xml:space="preserve">2036-03-11</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -27041,7 +27041,7 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandved 45</t>
+          <t xml:space="preserve">Dronning Margrethes Vej 13</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
@@ -27051,30 +27051,30 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t xml:space="preserve">5777338</t>
+          <t xml:space="preserve">5776972</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J361">
-        <v>1700</v>
+        <v>6714</v>
       </c>
       <c r="K361" t="inlineStr">
         <is>
-          <t xml:space="preserve">311886895</t>
+          <t xml:space="preserve">311888544</t>
         </is>
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ingeniørgruppen Haderslev ApS</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-11</t>
+          <t xml:space="preserve">2036-03-19</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -27116,7 +27116,7 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dronning Margrethes Vej 13</t>
+          <t xml:space="preserve">Stubbæk Skolegade 3</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
@@ -27126,7 +27126,7 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t xml:space="preserve">5776972</t>
+          <t xml:space="preserve">5265175</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -27135,11 +27135,11 @@
         </is>
       </c>
       <c r="J362">
-        <v>6714</v>
+        <v>1592</v>
       </c>
       <c r="K362" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888544</t>
+          <t xml:space="preserve">311888543</t>
         </is>
       </c>
       <c r="L362" t="inlineStr">
@@ -27206,11 +27206,11 @@
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J363">
-        <v>1592</v>
+        <v>120</v>
       </c>
       <c r="K363" t="inlineStr">
         <is>
@@ -27281,11 +27281,11 @@
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J364">
-        <v>120</v>
+        <v>723</v>
       </c>
       <c r="K364" t="inlineStr">
         <is>
@@ -27356,11 +27356,11 @@
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J365">
-        <v>723</v>
+        <v>2411</v>
       </c>
       <c r="K365" t="inlineStr">
         <is>
@@ -27431,11 +27431,11 @@
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J366">
-        <v>2411</v>
+        <v>192</v>
       </c>
       <c r="K366" t="inlineStr">
         <is>
@@ -27506,11 +27506,11 @@
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J367">
-        <v>192</v>
+        <v>145</v>
       </c>
       <c r="K367" t="inlineStr">
         <is>
@@ -27581,7 +27581,7 @@
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J368">
@@ -27656,7 +27656,7 @@
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J369">
@@ -27731,11 +27731,11 @@
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J370">
-        <v>145</v>
+        <v>110</v>
       </c>
       <c r="K370" t="inlineStr">
         <is>
@@ -27806,11 +27806,11 @@
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J371">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="K371" t="inlineStr">
         <is>
@@ -27851,12 +27851,12 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aabenraa Kommune</t>
+          <t xml:space="preserve">Museum Sønderjylland</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -27866,7 +27866,7 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stubbæk Skolegade 3</t>
+          <t xml:space="preserve">H P Hanssens Gade 33</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
@@ -27876,30 +27876,30 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t xml:space="preserve">5265175</t>
+          <t xml:space="preserve">5776368</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J372">
-        <v>105</v>
+        <v>839</v>
       </c>
       <c r="K372" t="inlineStr">
         <is>
-          <t xml:space="preserve">311888543</t>
+          <t xml:space="preserve">311929036</t>
         </is>
       </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Boligeftersyn Syd ApS</t>
         </is>
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-03-19</t>
+          <t xml:space="preserve">2036-09-30</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
